--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,41 +570,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -615,58 +615,58 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7K7K</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -674,15 +674,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -705,29 +705,29 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -746,41 +746,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A.T</t>
+          <t>7K7K</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -791,11 +791,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>A.T</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -813,23 +813,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -854,23 +854,23 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -885,41 +885,41 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -989,27 +989,27 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1020,52 +1020,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1087,15 +1087,15 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1140,73 +1140,73 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Man仔</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1214,19 +1214,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1245,52 +1245,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Man仔</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1320,40 +1320,40 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1376,21 +1376,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>emo</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1410,36 +1410,36 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>emo</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1455,11 +1455,11 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1470,41 +1470,41 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1515,29 +1515,29 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1545,112 +1545,112 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hoki</t>
+          <t>emo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>一只大虾</t>
+          <t>emo</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>丙辰</t>
+          <t>hoki</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1680,56 +1680,56 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>丙辰</t>
+          <t>一只大虾</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>12</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>7</v>
       </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -1740,29 +1740,29 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1770,122 +1770,122 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>伶伶</t>
+          <t>丙辰</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>佐伊</t>
+          <t>丙辰</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>余安懿</t>
+          <t>伶伶</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -1916,17 +1916,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>余安懿</t>
+          <t>佐伊</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1934,15 +1934,15 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -1965,25 +1965,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1995,32 +1995,32 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>余安懿</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2051,17 +2051,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>凤梨</t>
+          <t>余安懿</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2069,19 +2069,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2089,85 +2089,85 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>凤梨</t>
+          <t>余安懿</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
         <v>4</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>11</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>凤梨</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2220,11 +2220,11 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2235,37 +2235,37 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2280,41 +2280,41 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2355,73 +2355,73 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>十九</t>
+          <t>凤梨</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>十九</t>
+          <t>凤梨</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>9</v>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2429,15 +2429,15 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2445,97 +2445,97 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>十九</t>
+          <t>凤梨</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>十九</t>
+          <t>凤梨</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" t="n">
         <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2546,33 +2546,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>卓卓</t>
+          <t>十九</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2580,28 +2580,28 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>卓卓</t>
+          <t>十九</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2609,41 +2609,41 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>卓卓</t>
+          <t>十九</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
@@ -2654,56 +2654,56 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>卓卓</t>
+          <t>十九</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2730,13 +2730,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2744,27 +2744,27 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2793,15 +2793,15 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>周乏</t>
+          <t>卓卓</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2834,86 +2834,86 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>周乏</t>
+          <t>卓卓</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C55" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>卓卓</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
@@ -2924,60 +2924,60 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>园长</t>
+          <t>卓卓</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C57" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2985,310 +2985,310 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>园长</t>
+          <t>周乏</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>园长</t>
+          <t>周乏</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="n">
+        <v>42</v>
+      </c>
+      <c r="D59" t="n">
+        <v>21</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>21</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
         <v>5</v>
       </c>
-      <c r="C59" t="n">
-        <v>21</v>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>11</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>2</v>
-      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>园长</t>
+          <t>嘎嘎</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>夏夏</t>
+          <t>园长</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>大卫</t>
+          <t>园长</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>大道寺</t>
+          <t>园长</t>
         </is>
       </c>
       <c r="B63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>21</v>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
         <v>11</v>
       </c>
-      <c r="C63" t="n">
-        <v>3</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>3</v>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>大鹏</t>
+          <t>园长</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C64" t="n">
         <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -3300,77 +3300,77 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>妹妹</t>
+          <t>园长</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>妹妹</t>
+          <t>夏夏</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -3378,75 +3378,75 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>4</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>宁自</t>
+          <t>大卫</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>宁自</t>
+          <t>大道寺</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3468,15 +3468,15 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -3491,17 +3491,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>宝儿姐</t>
+          <t>大鹏</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3509,15 +3509,15 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3536,17 +3536,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>宝儿姐</t>
+          <t>妹妹</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -3570,25 +3570,25 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>妹妹</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
@@ -3599,11 +3599,11 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -3619,21 +3619,21 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>宁自</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
@@ -3644,11 +3644,11 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -3656,26 +3656,26 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>宁自</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C73" t="n">
         <v>3</v>
@@ -3693,19 +3693,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -3716,14 +3716,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>宝儿姐</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
         <v>4</v>
@@ -3734,41 +3734,41 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>小宇</t>
+          <t>宝儿姐</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3779,11 +3779,11 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -3806,17 +3806,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>小希</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="n">
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3824,19 +3824,19 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -3844,21 +3844,21 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>小希</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -3869,23 +3869,23 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -3896,37 +3896,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>小希</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C78" t="n">
         <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -3941,111 +3941,111 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B79" t="n">
+        <v>11</v>
+      </c>
+      <c r="C79" t="n">
+        <v>27</v>
+      </c>
+      <c r="D79" t="n">
         <v>5</v>
       </c>
-      <c r="C79" t="n">
-        <v>3</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小宇</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C80" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小希</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -4053,11 +4053,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4065,101 +4065,101 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小希</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小希</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C83" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4170,115 +4170,115 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C84" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>7</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
       <c r="H84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>小张哥</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B85" t="n">
+        <v>6</v>
+      </c>
+      <c r="C85" t="n">
+        <v>19</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
         <v>10</v>
       </c>
-      <c r="C85" t="n">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
         <v>4</v>
       </c>
-      <c r="D85" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>小张哥</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
         <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -4290,163 +4290,163 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>小张哥</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>小杀宝贝</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>小杀宝贝</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>小樱</t>
+          <t>小张哥</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4454,11 +4454,11 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -4470,25 +4470,25 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小张哥</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
         <v>3</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4515,52 +4515,52 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小张哥</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -4571,62 +4571,62 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小杀宝贝</t>
         </is>
       </c>
       <c r="B93" t="n">
+        <v>11</v>
+      </c>
+      <c r="C93" t="n">
+        <v>7</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>6</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
         <v>8</v>
       </c>
-      <c r="C93" t="n">
-        <v>57</v>
-      </c>
-      <c r="D93" t="n">
-        <v>27</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>59.3%</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>30</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>13</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>76.9%</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>32</v>
-      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小杀宝贝</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>12</v>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4638,37 +4638,37 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小樱</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -4679,44 +4679,44 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4724,158 +4724,158 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C97" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D97" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
         <v>8</v>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>25</v>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C98" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -4890,41 +4890,41 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>9</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -4935,258 +4935,258 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>小蓉</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>徐言雨</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
         <v>4</v>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>6</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H104" t="n">
-        <v>1</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>5</v>
-      </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C105" t="n">
         <v>6</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>4</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="H106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -5194,36 +5194,36 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C107" t="n">
         <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H107" t="n">
@@ -5235,28 +5235,28 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小蓉</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C108" t="n">
         <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5264,60 +5264,60 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小鲜</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C109" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F109" t="n">
-        <v>12</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="H109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -5325,56 +5325,56 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>徐言雨</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5385,295 +5385,295 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C111" t="n">
+        <v>13</v>
+      </c>
+      <c r="D111" t="n">
+        <v>5</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>8</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>3</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
         <v>6</v>
       </c>
-      <c r="D111" t="n">
-        <v>3</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>3</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="H111" t="n">
-        <v>1</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>4</v>
-      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C114" t="n">
         <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>李靖</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C115" t="n">
         <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>李靖</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B116" t="n">
+        <v>9</v>
+      </c>
+      <c r="C116" t="n">
+        <v>15</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>12</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
         <v>4</v>
       </c>
-      <c r="C116" t="n">
-        <v>3</v>
-      </c>
-      <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>2</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -5685,40 +5685,40 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -5726,44 +5726,44 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -5786,17 +5786,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -5804,15 +5804,15 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -5820,22 +5820,22 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C121" t="n">
         <v>3</v>
@@ -5857,81 +5857,81 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>桃子</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>5</v>
       </c>
       <c r="C122" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>桃子</t>
+          <t>李靖</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -5966,29 +5966,29 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>李靖</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C124" t="n">
         <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -6000,73 +6000,73 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C126" t="n">
         <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -6074,44 +6074,44 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>3</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>1</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C127" t="n">
         <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -6119,15 +6119,15 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6135,40 +6135,40 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C128" t="n">
         <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -6176,26 +6176,26 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C129" t="n">
         <v>3</v>
@@ -6213,11 +6213,11 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -6225,73 +6225,73 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C130" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D130" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>泡泡堂主</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -6299,23 +6299,23 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>浮玉</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -6336,64 +6336,64 @@
         <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C133" t="n">
         <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -6405,48 +6405,48 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C134" t="n">
         <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -6461,209 +6461,209 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C135" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>5</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
         <v>8</v>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>20</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H135" t="n">
-        <v>7</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="J135" t="n">
-        <v>22</v>
-      </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C136" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C137" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C138" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
         <v>6</v>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J138" t="n">
-        <v>20</v>
-      </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>牛肉干</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C139" t="n">
         <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -6675,73 +6675,73 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -6749,23 +6749,23 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J141" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -6776,56 +6776,56 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>泡泡堂主</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>浮玉</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C143" t="n">
         <v>3</v>
@@ -6843,64 +6843,64 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>2</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>3</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>2</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J143" t="n">
-        <v>4</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C144" t="n">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -6911,11 +6911,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C145" t="n">
         <v>3</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -6933,19 +6933,19 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -6956,78 +6956,78 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -7035,142 +7035,142 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B149" t="n">
+        <v>8</v>
+      </c>
+      <c r="C149" t="n">
+        <v>26</v>
+      </c>
+      <c r="D149" t="n">
         <v>9</v>
       </c>
-      <c r="C149" t="n">
-        <v>3</v>
-      </c>
-      <c r="D149" t="n">
-        <v>0</v>
-      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>牛肉干</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C150" t="n">
         <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -7181,17 +7181,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C151" t="n">
         <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -7199,11 +7199,11 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -7219,21 +7219,21 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
         <v>1</v>
@@ -7244,11 +7244,11 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -7260,118 +7260,118 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C153" t="n">
+        <v>3</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>3</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
         <v>6</v>
       </c>
-      <c r="D153" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>6</v>
-      </c>
-      <c r="G153" t="inlineStr">
+      <c r="K153" t="inlineStr">
         <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="H153" t="n">
-        <v>2</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J153" t="n">
-        <v>7</v>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7379,15 +7379,15 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -7406,107 +7406,107 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>翼风</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C156" t="n">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>艺术家</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="n">
+        <v>118</v>
+      </c>
+      <c r="D157" t="n">
+        <v>45</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>48.9%</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>73</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>45.2%</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
         <v>10</v>
       </c>
-      <c r="C157" t="n">
-        <v>3</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>3</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H157" t="n">
-        <v>0</v>
-      </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C158" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -7514,11 +7514,11 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H158" t="n">
@@ -7530,28 +7530,28 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -7559,11 +7559,11 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -7575,85 +7575,85 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
         <v>1</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>2</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>4</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t>75.0%</t>
-        </is>
-      </c>
-      <c r="H160" t="n">
-        <v>4</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J160" t="n">
-        <v>11</v>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>36.4%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C161" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H161" t="n">
@@ -7665,18 +7665,18 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -7721,119 +7721,119 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>谢朵儿</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C163" t="n">
         <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C164" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C165" t="n">
         <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H165" t="n">
@@ -7845,28 +7845,28 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>9</v>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -7874,15 +7874,15 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -7890,216 +7890,216 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>10</v>
       </c>
       <c r="C167" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
         <v>2</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F168" t="n">
+        <v>3</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>3</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
         <v>4</v>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H168" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J168" t="n">
-        <v>5</v>
-      </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>翼风</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C169" t="n">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="D169" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>艺术家</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C170" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C171" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D171" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8115,40 +8115,40 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>钟杰</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C172" t="n">
         <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H172" t="n">
@@ -8160,44 +8160,44 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>阿函</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -8205,44 +8205,44 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B174" t="n">
+        <v>4</v>
+      </c>
+      <c r="C174" t="n">
+        <v>6</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
         <v>5</v>
       </c>
-      <c r="C174" t="n">
-        <v>3</v>
-      </c>
-      <c r="D174" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>2</v>
-      </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8250,67 +8250,67 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B175" t="n">
+        <v>9</v>
+      </c>
+      <c r="C175" t="n">
         <v>6</v>
       </c>
-      <c r="C175" t="n">
-        <v>12</v>
-      </c>
       <c r="D175" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C176" t="n">
         <v>3</v>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H176" t="n">
@@ -8336,11 +8336,11 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -8351,11 +8351,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>谢朵儿</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C177" t="n">
         <v>3</v>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -8396,25 +8396,25 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C178" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D178" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -8426,32 +8426,32 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>雨神末路</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C179" t="n">
         <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8459,11 +8459,11 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H179" t="n">
@@ -8475,54 +8475,684 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
+          <t>豪哥哥</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>9</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>2</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>豪哥哥</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>10</v>
+      </c>
+      <c r="C181" t="n">
+        <v>6</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>4</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>2</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>4</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>豪哥哥</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>12</v>
+      </c>
+      <c r="C182" t="n">
+        <v>7</v>
+      </c>
+      <c r="D182" t="n">
+        <v>3</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>4</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>5</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>郭小炜</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>6</v>
+      </c>
+      <c r="C183" t="n">
+        <v>29</v>
+      </c>
+      <c r="D183" t="n">
+        <v>8</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>21</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>7</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>21</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>郭小炜</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>7</v>
+      </c>
+      <c r="C184" t="n">
+        <v>9</v>
+      </c>
+      <c r="D184" t="n">
+        <v>4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>5</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>2</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>2</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>郭小炜</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>8</v>
+      </c>
+      <c r="C185" t="n">
+        <v>26</v>
+      </c>
+      <c r="D185" t="n">
+        <v>11</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>15</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>6</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>20</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>钟杰</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>11</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>2</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>阿函</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>12</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>3</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>2</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>6</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>5</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>2</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>6</v>
+      </c>
+      <c r="C189" t="n">
+        <v>12</v>
+      </c>
+      <c r="D189" t="n">
+        <v>7</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>5</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>10</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>7</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>2</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>8</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>2</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>9</v>
+      </c>
+      <c r="C192" t="n">
+        <v>18</v>
+      </c>
+      <c r="D192" t="n">
+        <v>10</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>8</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>3</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>10</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>雨神末路</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>11</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
           <t>鼓鼓</t>
         </is>
       </c>
-      <c r="B180" t="n">
+      <c r="B194" t="n">
         <v>10</v>
       </c>
-      <c r="C180" t="n">
-        <v>3</v>
-      </c>
-      <c r="D180" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F180" t="n">
-        <v>2</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H180" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J180" t="n">
+      <c r="C194" t="n">
+        <v>3</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>2</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
         <v>4</v>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="K194" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>

--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J183" t="n">

--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J183" t="n">

--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K194"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,38 +528,38 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>9</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>8</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -809,38 +809,38 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>A.T</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -858,23 +858,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -899,23 +899,23 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -930,41 +930,41 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -975,17 +975,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1034,27 +1034,27 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1065,52 +1065,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -1132,15 +1132,15 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1185,73 +1185,73 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Man仔</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1290,52 +1290,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Man仔</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1365,40 +1365,40 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1410,11 +1410,11 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1425,29 +1425,29 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1455,44 +1455,44 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emo</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1529,15 +1529,15 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1545,11 +1545,11 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1560,41 +1560,41 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1605,52 +1605,52 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hoki</t>
+          <t>emo</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1680,28 +1680,28 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>一只大虾</t>
+          <t>hoki</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1709,44 +1709,44 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>丙辰</t>
+          <t>一只大虾</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1754,27 +1754,27 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -1785,41 +1785,41 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1830,29 +1830,29 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1860,73 +1860,73 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>伶伶</t>
+          <t>丙辰</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>佐伊</t>
+          <t>伶伶</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1938,15 +1938,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -1954,14 +1954,14 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>余安懿</t>
+          <t>佐伊</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1983,23 +1983,23 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2010,29 +2010,29 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2055,25 +2055,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
@@ -2122,48 +2122,48 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>余安懿</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>11</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2175,36 +2175,36 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>凤梨</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2235,37 +2235,37 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2339,15 +2339,15 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2384,11 +2384,11 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -2400,11 +2400,11 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2460,41 +2460,41 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2505,86 +2505,86 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>十九</t>
+          <t>凤梨</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C48" t="n">
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2595,25 +2595,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2625,11 +2625,11 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2654,23 +2654,23 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2726,29 +2726,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>卓卓</t>
+          <t>十九</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2760,11 +2760,11 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2789,27 +2789,27 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2820,41 +2820,41 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>4</v>
       </c>
-      <c r="C54" t="n">
-        <v>6</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
         <v>5</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>3</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>7</v>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>2</v>
@@ -2879,11 +2879,11 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -2895,11 +2895,11 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2924,27 +2924,27 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C57" t="n">
         <v>6</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2985,28 +2985,28 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>周乏</t>
+          <t>卓卓</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3014,23 +3014,23 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3041,62 +3041,62 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>周乏</t>
+          <t>卓卓</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C59" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
         <v>5</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>26</v>
-      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>周乏</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3120,93 +3120,93 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>园长</t>
+          <t>周乏</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
         <v>44</v>
       </c>
       <c r="D61" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>园长</t>
+          <t>嘎嘎</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
         <v>2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -3225,41 +3225,41 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -3270,13 +3270,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3284,23 +3284,23 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3315,152 +3315,152 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C65" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D65" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>夏夏</t>
+          <t>园长</t>
         </is>
       </c>
       <c r="B66" t="n">
+        <v>7</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
         <v>4</v>
       </c>
-      <c r="C66" t="n">
-        <v>6</v>
-      </c>
-      <c r="D66" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>3</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>3</v>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>大卫</t>
+          <t>园长</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>大道寺</t>
+          <t>夏夏</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -3468,85 +3468,85 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>3</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>3</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>大鹏</t>
+          <t>大卫</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>妹妹</t>
+          <t>大道寺</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3558,19 +3558,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3581,62 +3581,62 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>妹妹</t>
+          <t>大鹏</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>宁自</t>
+          <t>大鹏</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
         <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3660,28 +3660,28 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>宁自</t>
+          <t>妹妹</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -3716,62 +3716,62 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>宝儿姐</t>
+          <t>妹妹</t>
         </is>
       </c>
       <c r="B74" t="n">
+        <v>5</v>
+      </c>
+      <c r="C74" t="n">
         <v>4</v>
       </c>
-      <c r="C74" t="n">
-        <v>7</v>
-      </c>
       <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
         <v>4</v>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>3</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>3</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>3</v>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>宝儿姐</t>
+          <t>宁自</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C75" t="n">
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3779,15 +3779,15 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3795,28 +3795,28 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>宁自</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C76" t="n">
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3824,44 +3824,44 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>宝儿姐</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3869,38 +3869,38 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>宝儿姐</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C78" t="n">
         <v>3</v>
@@ -3918,23 +3918,23 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3945,13 +3945,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3959,44 +3959,44 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>小宇</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4004,64 +4004,64 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>小希</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4076,17 +4076,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>小希</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4094,56 +4094,56 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>小希</t>
+          <t>小宇</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -4155,22 +4155,22 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小希</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
         <v>3</v>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4200,85 +4200,85 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小希</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小希</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -4305,41 +4305,41 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C87" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4350,41 +4350,41 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88" t="n">
+        <v>20</v>
+      </c>
+      <c r="D88" t="n">
+        <v>9</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>11</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>5</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
         <v>16</v>
       </c>
-      <c r="D88" t="n">
-        <v>4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>12</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>9</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>21</v>
-      </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -4395,13 +4395,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C89" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4409,236 +4409,236 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>小张哥</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B90" t="n">
+        <v>9</v>
+      </c>
+      <c r="C90" t="n">
+        <v>23</v>
+      </c>
+      <c r="D90" t="n">
         <v>10</v>
       </c>
-      <c r="C90" t="n">
-        <v>4</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2</v>
-      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>小张哥</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>小张哥</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>小杀宝贝</t>
+          <t>小张哥</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>小杀宝贝</t>
+          <t>小张哥</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -4650,32 +4650,32 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>小樱</t>
+          <t>小张哥</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -4687,36 +4687,36 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小杀宝贝</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4724,56 +4724,56 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小杀宝贝</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C97" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -4785,56 +4785,56 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小樱</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C98" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4845,176 +4845,176 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C102" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5025,41 +5025,41 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v>18</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>38.9%</t>
-        </is>
-      </c>
       <c r="H103" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -5070,29 +5070,29 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D104" t="n">
         <v>3</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5100,11 +5100,11 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -5115,25 +5115,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -5141,15 +5141,15 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -5160,41 +5160,41 @@
         </is>
       </c>
       <c r="B106" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" t="n">
+        <v>21</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>18</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
         <v>10</v>
       </c>
-      <c r="C106" t="n">
-        <v>3</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>3</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
-        <v>1</v>
-      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -5205,97 +5205,97 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>小蓉</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>小鲜</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C109" t="n">
         <v>3</v>
@@ -5325,118 +5325,118 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>徐言雨</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小米粥</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C111" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小蓉</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5444,52 +5444,52 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小蓉</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5497,15 +5497,15 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -5516,90 +5516,90 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>小鲜</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C114" t="n">
         <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>徐言雨</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C115" t="n">
         <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5610,41 +5610,41 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C116" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>8</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>3</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>6</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>12</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
-        <v>4</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>13</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -5655,25 +5655,25 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C117" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -5685,11 +5685,11 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5700,33 +5700,33 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D118" t="n">
         <v>3</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -5734,18 +5734,18 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C119" t="n">
         <v>2</v>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -5763,44 +5763,44 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -5831,17 +5831,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C121" t="n">
         <v>3</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -5849,60 +5849,60 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D122" t="n">
         <v>3</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>12</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F122" t="n">
-        <v>3</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -5910,36 +5910,36 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>李靖</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5947,123 +5947,123 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>李靖</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B124" t="n">
+        <v>11</v>
+      </c>
+      <c r="C124" t="n">
+        <v>6</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
         <v>4</v>
       </c>
-      <c r="C124" t="n">
-        <v>3</v>
-      </c>
-      <c r="D124" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>2</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>2</v>
-      </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
         <v>1</v>
@@ -6074,15 +6074,15 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6090,28 +6090,28 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -6119,11 +6119,11 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -6146,21 +6146,21 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -6176,26 +6176,26 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李靖</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
         <v>3</v>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -6217,142 +6217,142 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>桃子</t>
+          <t>李靖</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>桃子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C132" t="n">
         <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6360,44 +6360,44 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -6416,11 +6416,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C134" t="n">
         <v>3</v>
@@ -6438,30 +6438,30 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -6471,101 +6471,101 @@
         <v>6</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -6573,48 +6573,48 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C138" t="n">
         <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -6630,22 +6630,22 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C139" t="n">
         <v>3</v>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -6686,62 +6686,62 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C140" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>11</v>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -6749,11 +6749,11 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -6765,22 +6765,22 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>泡泡堂主</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -6821,62 +6821,62 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>浮玉</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C143" t="n">
         <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C144" t="n">
         <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -6900,22 +6900,22 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C145" t="n">
         <v>3</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -6956,205 +6956,205 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C146" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D146" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C147" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>泡泡堂主</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C148" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>浮玉</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C149" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J149" t="n">
-        <v>24</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>牛肉干</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C150" t="n">
         <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -7170,22 +7170,22 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C151" t="n">
         <v>3</v>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -7226,332 +7226,332 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C154" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>牛肉干</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C156" t="n">
         <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C157" t="n">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="D157" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
         <v>1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -7559,11 +7559,11 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -7575,25 +7575,25 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D160" t="n">
         <v>1</v>
@@ -7604,60 +7604,60 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -7665,22 +7665,22 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C162" t="n">
         <v>3</v>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H162" t="n">
@@ -7710,73 +7710,73 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C164" t="n">
         <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -7784,19 +7784,19 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -7804,36 +7804,36 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>12</v>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
         <v>1</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H165" t="n">
@@ -7845,28 +7845,28 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -7874,11 +7874,11 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H166" t="n">
@@ -7886,26 +7886,26 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J166" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C167" t="n">
         <v>3</v>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C168" t="n">
         <v>3</v>
@@ -7972,75 +7972,75 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>翼风</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C169" t="n">
-        <v>118</v>
+        <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>艺术家</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C170" t="n">
         <v>3</v>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H170" t="n">
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -8081,59 +8081,59 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C171" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -8144,44 +8144,44 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C173" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -8189,124 +8189,124 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B174" t="n">
+        <v>11</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>3</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
         <v>4</v>
       </c>
-      <c r="C174" t="n">
-        <v>6</v>
-      </c>
-      <c r="D174" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>5</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="H174" t="n">
-        <v>1</v>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J174" t="n">
-        <v>6</v>
-      </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>翼风</t>
         </is>
       </c>
       <c r="B175" t="n">
+        <v>7</v>
+      </c>
+      <c r="C175" t="n">
+        <v>123</v>
+      </c>
+      <c r="D175" t="n">
+        <v>58</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>72.4%</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>65</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>64.6%</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
         <v>9</v>
       </c>
-      <c r="C175" t="n">
-        <v>6</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>6</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H175" t="n">
-        <v>3</v>
-      </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>艺术家</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -8316,7 +8316,7 @@
         <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -8324,15 +8324,15 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8340,40 +8340,40 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>谢朵儿</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H177" t="n">
@@ -8385,130 +8385,130 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C178" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D180" t="n">
         <v>1</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H180" t="n">
@@ -8516,93 +8516,93 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C181" t="n">
         <v>6</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C182" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8610,73 +8610,73 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C183" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>谢朵儿</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C184" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -8684,15 +8684,15 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -8704,63 +8704,63 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C185" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D185" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>3</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="H185" t="n">
-        <v>6</v>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="J185" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>钟杰</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C186" t="n">
         <v>3</v>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H186" t="n">
@@ -8794,24 +8794,24 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>阿函</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C187" t="n">
         <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -8819,68 +8819,68 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -8891,41 +8891,41 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C189" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D189" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F189" t="n">
+        <v>4</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
         <v>5</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="H189" t="n">
-        <v>1</v>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J189" t="n">
-        <v>10</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -8936,62 +8936,62 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -8999,19 +8999,19 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -9019,59 +9019,59 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C192" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F192" t="n">
+        <v>16</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
         <v>8</v>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H192" t="n">
-        <v>3</v>
-      </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>雨神末路</t>
+          <t>钟杰</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -9081,15 +9081,15 @@
         <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -9105,54 +9105,369 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
+          <t>阿函</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>12</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>3</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>6</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>5</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>2</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>6</v>
+      </c>
+      <c r="C196" t="n">
+        <v>12</v>
+      </c>
+      <c r="D196" t="n">
+        <v>7</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>5</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>10</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>7</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>2</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>8</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>2</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>9</v>
+      </c>
+      <c r="C199" t="n">
+        <v>18</v>
+      </c>
+      <c r="D199" t="n">
+        <v>10</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>8</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>3</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>10</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>雨神末路</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>11</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>2</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
           <t>鼓鼓</t>
         </is>
       </c>
-      <c r="B194" t="n">
+      <c r="B201" t="n">
         <v>10</v>
       </c>
-      <c r="C194" t="n">
-        <v>3</v>
-      </c>
-      <c r="D194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F194" t="n">
-        <v>2</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H194" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J194" t="n">
+      <c r="C201" t="n">
+        <v>3</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>2</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
         <v>4</v>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="K201" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>

--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K201"/>
+  <dimension ref="A1:K205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -539,11 +539,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -573,10 +573,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -584,15 +584,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -600,11 +600,11 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -798,22 +798,22 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1781,11 +1781,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>丙辰</t>
+          <t>一心</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1815,11 +1815,11 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1830,41 +1830,41 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1875,29 +1875,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1905,73 +1905,73 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>伶伶</t>
+          <t>丙辰</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>佐伊</t>
+          <t>伶伶</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1983,15 +1983,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -1999,14 +1999,14 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>余安懿</t>
+          <t>佐伊</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2028,23 +2028,23 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2055,29 +2055,29 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2100,25 +2100,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" t="n">
         <v>3</v>
@@ -2167,48 +2167,48 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>余安懿</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>11</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2220,36 +2220,36 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>凤梨</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2384,15 +2384,15 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2429,11 +2429,11 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -2445,11 +2445,11 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2478,23 +2478,23 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2505,41 +2505,41 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2550,86 +2550,86 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>十九</t>
+          <t>凤梨</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C49" t="n">
         <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2640,25 +2640,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -2670,11 +2670,11 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2699,23 +2699,23 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2756,11 +2756,11 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -2771,29 +2771,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>卓卓</t>
+          <t>十九</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -2805,11 +2805,11 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2820,13 +2820,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2834,27 +2834,27 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2865,41 +2865,41 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2910,29 +2910,29 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2940,11 +2940,11 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2955,29 +2955,29 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
         <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -3000,41 +3000,41 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D59" t="n">
         <v>2</v>
@@ -3059,44 +3059,44 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>周乏</t>
+          <t>卓卓</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3104,27 +3104,27 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -3135,131 +3135,131 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>嘎嘎</t>
+          <t>周乏</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>园长</t>
+          <t>嘎嘎</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -3270,41 +3270,41 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -3315,25 +3315,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -3345,11 +3345,11 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3360,33 +3360,33 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3405,221 +3405,221 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C67" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>夏夏</t>
+          <t>园长</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>90.5%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>大卫</t>
+          <t>夏夏</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>大道寺</t>
+          <t>大卫</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>大鹏</t>
+          <t>大道寺</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C71" t="n">
         <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
         <v>3</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -3671,17 +3671,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>妹妹</t>
+          <t>大鹏</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3689,11 +3689,11 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -3705,11 +3705,11 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74" t="n">
         <v>4</v>
@@ -3738,37 +3738,37 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>宁自</t>
+          <t>妹妹</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>5</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -3779,27 +3779,27 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3810,13 +3810,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C76" t="n">
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3824,15 +3824,15 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3840,28 +3840,28 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>宝儿姐</t>
+          <t>宁自</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3873,11 +3873,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3941,17 +3941,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>宝儿姐</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3959,27 +3959,27 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
@@ -4004,15 +4004,15 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -4035,29 +4035,29 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4080,58 +4080,58 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
         <v>5</v>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>22</v>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>小宇</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4139,41 +4139,41 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>小希</t>
+          <t>小宇</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -4184,15 +4184,15 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4200,11 +4200,11 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4215,13 +4215,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
         <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4229,15 +4229,15 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
         <v>3</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -4290,18 +4290,18 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小希</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4311,19 +4311,19 @@
         <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4350,41 +4350,41 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4395,41 +4395,41 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -4440,41 +4440,41 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C90" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4485,41 +4485,41 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>9</v>
+      </c>
+      <c r="C91" t="n">
+        <v>23</v>
+      </c>
+      <c r="D91" t="n">
         <v>10</v>
       </c>
-      <c r="C91" t="n">
-        <v>16</v>
-      </c>
-      <c r="D91" t="n">
-        <v>4</v>
-      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -4530,86 +4530,86 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C92" t="n">
         <v>16</v>
       </c>
       <c r="D92" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>12</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
         <v>9</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>7</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>5</v>
-      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>小张哥</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C93" t="n">
+        <v>16</v>
+      </c>
+      <c r="D93" t="n">
+        <v>9</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>7</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>5</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
         <v>4</v>
       </c>
-      <c r="D93" t="n">
-        <v>2</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>1</v>
-      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4620,25 +4620,25 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -4650,11 +4650,11 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4665,13 +4665,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4687,36 +4687,36 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>小杀宝贝</t>
+          <t>小张哥</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4724,11 +4724,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -4740,11 +4740,11 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4777,33 +4777,33 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>小樱</t>
+          <t>小杀宝贝</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4814,11 +4814,11 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -4830,36 +4830,36 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小樱</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4875,11 +4875,11 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4890,25 +4890,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -4920,11 +4920,11 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4935,41 +4935,41 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>6</v>
+      </c>
+      <c r="C101" t="n">
+        <v>12</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>8</v>
       </c>
-      <c r="C101" t="n">
-        <v>65</v>
-      </c>
-      <c r="D101" t="n">
-        <v>29</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>58.6%</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>36</v>
-      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4980,58 +4980,58 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -5039,11 +5039,11 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -5055,11 +5055,11 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5070,41 +5070,41 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F104" t="n">
-        <v>9</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>77.8%</t>
-        </is>
-      </c>
       <c r="H104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -5115,41 +5115,41 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C105" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -5160,41 +5160,41 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C106" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>26</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>18</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>38.9%</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
-        <v>10</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
       <c r="J106" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -5205,41 +5205,41 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D107" t="n">
         <v>3</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -5250,41 +5250,41 @@
         </is>
       </c>
       <c r="B108" t="n">
+        <v>5</v>
+      </c>
+      <c r="C108" t="n">
         <v>9</v>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
         <v>6</v>
       </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>5</v>
-      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5295,41 +5295,41 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -5340,13 +5340,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5354,56 +5354,56 @@
         </is>
       </c>
       <c r="F110" t="n">
+        <v>3</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
         <v>4</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>3</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>小米粥</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -5415,40 +5415,40 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>小蓉</t>
+          <t>小米粥</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C113" t="n">
         <v>3</v>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -5516,17 +5516,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>小鲜</t>
+          <t>小蓉</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C114" t="n">
         <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -5534,23 +5534,23 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -5561,29 +5561,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>徐言雨</t>
+          <t>小鲜</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C115" t="n">
         <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -5606,45 +5606,45 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>徐言雨</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C116" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5655,41 +5655,41 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117" t="n">
+        <v>13</v>
+      </c>
+      <c r="D117" t="n">
+        <v>5</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>8</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>3</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
         <v>6</v>
       </c>
-      <c r="D117" t="n">
-        <v>2</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>4</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H117" t="n">
-        <v>2</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>4</v>
-      </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5700,17 +5700,17 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5745,41 +5745,41 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5790,21 +5790,21 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -5835,41 +5835,41 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C121" t="n">
         <v>3</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5880,21 +5880,21 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C122" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5902,19 +5902,19 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5925,41 +5925,41 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C123" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D123" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -5970,66 +5970,66 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6045,36 +6045,36 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6090,11 +6090,11 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6105,25 +6105,25 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
         <v>1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -6150,52 +6150,52 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>李靖</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129" t="n">
         <v>3</v>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -6236,101 +6236,101 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>李靖</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李靖</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李靖</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C132" t="n">
         <v>3</v>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6375,13 +6375,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6389,27 +6389,27 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C134" t="n">
         <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -6434,27 +6434,27 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>3</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H134" t="n">
-        <v>1</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J134" t="n">
-        <v>9</v>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -6465,25 +6465,25 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C135" t="n">
         <v>6</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -6491,40 +6491,40 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>桃子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C136" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -6532,126 +6532,126 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>桃子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D137" t="n">
         <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -6659,11 +6659,11 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -6690,41 +6690,41 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C140" t="n">
         <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6735,25 +6735,25 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -6765,11 +6765,11 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6780,13 +6780,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -6794,23 +6794,23 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -6821,41 +6821,41 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B143" t="n">
+        <v>11</v>
+      </c>
+      <c r="C143" t="n">
+        <v>6</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
         <v>5</v>
       </c>
-      <c r="C143" t="n">
-        <v>3</v>
-      </c>
-      <c r="D143" t="n">
-        <v>2</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>1</v>
-      </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -6866,11 +6866,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C144" t="n">
         <v>3</v>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -6900,11 +6900,11 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6915,41 +6915,41 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C145" t="n">
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6960,41 +6960,41 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C146" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -7005,13 +7005,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C147" t="n">
         <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -7019,11 +7019,11 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -7039,63 +7039,63 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>泡泡堂主</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>浮玉</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C149" t="n">
         <v>3</v>
@@ -7113,15 +7113,15 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -7136,17 +7136,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C150" t="n">
         <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -7154,38 +7154,38 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>泡泡堂主</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C151" t="n">
         <v>3</v>
@@ -7207,15 +7207,15 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -7226,135 +7226,135 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>浮玉</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C152" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C153" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C154" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7365,25 +7365,25 @@
         </is>
       </c>
       <c r="B155" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" t="n">
+        <v>31</v>
+      </c>
+      <c r="D155" t="n">
         <v>8</v>
       </c>
-      <c r="C155" t="n">
-        <v>28</v>
-      </c>
-      <c r="D155" t="n">
-        <v>9</v>
-      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="H155" t="n">
@@ -7395,153 +7395,153 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>牛肉干</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C157" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>牛肉干</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -7551,19 +7551,19 @@
         <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -7575,11 +7575,11 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7590,21 +7590,21 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C160" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -7612,19 +7612,19 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7635,25 +7635,25 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C161" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
         <v>1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H161" t="n">
@@ -7665,11 +7665,11 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C162" t="n">
         <v>3</v>
@@ -7698,82 +7698,82 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>6</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
-        <v>2</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J162" t="n">
-        <v>4</v>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C163" t="n">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="D163" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D164" t="n">
         <v>1</v>
@@ -7784,44 +7784,44 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -7829,79 +7829,79 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="J166" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -7911,19 +7911,19 @@
         <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H167" t="n">
@@ -7931,11 +7931,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -7946,17 +7946,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -7964,27 +7964,27 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7995,13 +7995,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C169" t="n">
         <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -8009,11 +8009,11 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H169" t="n">
@@ -8025,11 +8025,11 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8040,17 +8040,17 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -8058,23 +8058,23 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -8085,55 +8085,55 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C171" t="n">
         <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -8156,44 +8156,44 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C173" t="n">
         <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H173" t="n">
@@ -8205,44 +8205,44 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C174" t="n">
         <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8250,77 +8250,77 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>翼风</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B175" t="n">
+        <v>9</v>
+      </c>
+      <c r="C175" t="n">
+        <v>6</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>6</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>2</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
         <v>7</v>
       </c>
-      <c r="C175" t="n">
-        <v>123</v>
-      </c>
-      <c r="D175" t="n">
-        <v>58</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>72.4%</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>65</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>64.6%</t>
-        </is>
-      </c>
-      <c r="H175" t="n">
-        <v>9</v>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="J175" t="n">
-        <v>33</v>
-      </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>艺术家</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>10</v>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H176" t="n">
@@ -8340,25 +8340,25 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C177" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -8369,19 +8369,19 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -8389,104 +8389,104 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>翼风</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>91.4%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>艺术家</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C179" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -8496,19 +8496,19 @@
         <v>6</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H180" t="n">
@@ -8516,29 +8516,29 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C181" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -8549,72 +8549,72 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J182" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -8625,29 +8625,29 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D183" t="n">
         <v>1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -8655,81 +8655,81 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>谢朵儿</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C185" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -8737,36 +8737,36 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J185" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C186" t="n">
         <v>3</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -8774,11 +8774,11 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H186" t="n">
@@ -8790,40 +8790,40 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>谢朵儿</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C187" t="n">
         <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H187" t="n">
@@ -8846,29 +8846,29 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>谢朵儿</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C188" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H188" t="n">
@@ -8876,11 +8876,11 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J188" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -8895,119 +8895,119 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C189" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F189" t="n">
+        <v>6</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>3</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
         <v>4</v>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H189" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J189" t="n">
-        <v>5</v>
-      </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C190" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C191" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -9019,81 +9019,81 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C192" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D192" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>钟杰</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H193" t="n">
@@ -9105,97 +9105,97 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>阿函</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B194" t="n">
+        <v>6</v>
+      </c>
+      <c r="C194" t="n">
+        <v>39</v>
+      </c>
+      <c r="D194" t="n">
+        <v>11</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>28</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
         <v>12</v>
       </c>
-      <c r="C194" t="n">
-        <v>3</v>
-      </c>
-      <c r="D194" t="n">
-        <v>0</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F194" t="n">
-        <v>3</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H194" t="n">
-        <v>2</v>
-      </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B195" t="n">
+        <v>7</v>
+      </c>
+      <c r="C195" t="n">
+        <v>9</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
         <v>5</v>
       </c>
-      <c r="C195" t="n">
-        <v>3</v>
-      </c>
-      <c r="D195" t="n">
-        <v>1</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F195" t="n">
-        <v>2</v>
-      </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -9206,70 +9206,70 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C196" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D196" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>钟杰</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C197" t="n">
         <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -9277,11 +9277,11 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -9296,45 +9296,45 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>阿函</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C198" t="n">
         <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -9345,74 +9345,74 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C199" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D199" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>雨神末路</t>
+          <t>陈俊洁</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -9420,54 +9420,234 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>7</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>2</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>1</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>2</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>8</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>2</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>9</v>
+      </c>
+      <c r="C203" t="n">
+        <v>18</v>
+      </c>
+      <c r="D203" t="n">
+        <v>10</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>8</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>3</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>10</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>雨神末路</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>11</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
           <t>鼓鼓</t>
         </is>
       </c>
-      <c r="B201" t="n">
+      <c r="B205" t="n">
         <v>10</v>
       </c>
-      <c r="C201" t="n">
-        <v>3</v>
-      </c>
-      <c r="D201" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F201" t="n">
-        <v>2</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H201" t="n">
-        <v>0</v>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J201" t="n">
+      <c r="C205" t="n">
+        <v>3</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
         <v>4</v>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="K205" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>

--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:K208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3453,7 +3453,7 @@
         <v>12</v>
       </c>
       <c r="C68" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D68" t="n">
         <v>27</v>
@@ -3464,11 +3464,11 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -3480,11 +3480,11 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -4578,22 +4578,22 @@
         <v>11</v>
       </c>
       <c r="C93" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="C101" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D101" t="n">
         <v>4</v>
@@ -4949,11 +4949,11 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -4965,11 +4965,11 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -5430,25 +5430,25 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C112" t="n">
         <v>2</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -5460,40 +5460,40 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>小蓉</t>
+          <t>小米粥</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -5505,11 +5505,11 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C114" t="n">
         <v>3</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -5561,17 +5561,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>小鲜</t>
+          <t>小蓉</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C115" t="n">
         <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -5579,23 +5579,23 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -5606,29 +5606,29 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>徐言雨</t>
+          <t>小鲜</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C116" t="n">
         <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -5651,45 +5651,45 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>徐言雨</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C117" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5700,41 +5700,41 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118" t="n">
+        <v>13</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>8</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>3</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
         <v>6</v>
       </c>
-      <c r="D118" t="n">
-        <v>2</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>4</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H118" t="n">
-        <v>2</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>4</v>
-      </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5745,17 +5745,17 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5790,41 +5790,41 @@
         </is>
       </c>
       <c r="B120" t="n">
+        <v>4</v>
+      </c>
+      <c r="C120" t="n">
+        <v>9</v>
+      </c>
+      <c r="D120" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
         <v>5</v>
       </c>
-      <c r="C120" t="n">
-        <v>2</v>
-      </c>
-      <c r="D120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>1</v>
-      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -5880,41 +5880,41 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C122" t="n">
         <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5925,21 +5925,21 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C123" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5947,19 +5947,19 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5970,41 +5970,41 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C124" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D124" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -6015,41 +6015,41 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6060,62 +6060,62 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -6123,19 +6123,19 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6150,41 +6150,41 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -6209,27 +6209,27 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6240,25 +6240,25 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -6270,40 +6270,40 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>李靖</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -6315,11 +6315,11 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C132" t="n">
         <v>3</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -6352,11 +6352,11 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -6364,24 +6364,24 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李靖</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6389,27 +6389,27 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="B134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C134" t="n">
         <v>5</v>
       </c>
-      <c r="C134" t="n">
-        <v>3</v>
-      </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -6434,27 +6434,27 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -6479,11 +6479,11 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -6495,11 +6495,11 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -6510,13 +6510,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -6540,11 +6540,11 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6555,86 +6555,86 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C137" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>3</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F137" t="n">
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
         <v>9</v>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>55.6%</t>
-        </is>
-      </c>
-      <c r="H137" t="n">
-        <v>2</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J137" t="n">
-        <v>8</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>桃子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C138" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D138" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J138" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6645,58 +6645,58 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -6720,11 +6720,11 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C141" t="n">
         <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -6749,11 +6749,11 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -6765,11 +6765,11 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6780,33 +6780,33 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -6825,13 +6825,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C143" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -6839,27 +6839,27 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6870,13 +6870,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -6900,52 +6900,52 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B145" t="n">
+        <v>11</v>
+      </c>
+      <c r="C145" t="n">
+        <v>6</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
         <v>5</v>
       </c>
-      <c r="C145" t="n">
-        <v>3</v>
-      </c>
-      <c r="D145" t="n">
-        <v>2</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>1</v>
-      </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -6956,11 +6956,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C146" t="n">
         <v>3</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H146" t="n">
@@ -6990,11 +6990,11 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7005,41 +7005,41 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C147" t="n">
         <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7050,41 +7050,41 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C148" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -7095,13 +7095,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C149" t="n">
         <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -7109,11 +7109,11 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H149" t="n">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7140,25 +7140,25 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H150" t="n">
@@ -7166,77 +7166,77 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>泡泡堂主</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C151" t="n">
         <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>浮玉</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C152" t="n">
         <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -7244,11 +7244,11 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -7271,37 +7271,37 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>泡泡堂主</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C153" t="n">
         <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -7309,142 +7309,142 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>浮玉</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C154" t="n">
         <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C155" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C156" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7455,41 +7455,41 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C157" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7500,25 +7500,25 @@
         </is>
       </c>
       <c r="B158" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" t="n">
+        <v>31</v>
+      </c>
+      <c r="D158" t="n">
         <v>8</v>
       </c>
-      <c r="C158" t="n">
-        <v>28</v>
-      </c>
-      <c r="D158" t="n">
-        <v>9</v>
-      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="H158" t="n">
@@ -7530,153 +7530,153 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>牛肉干</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C160" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>牛肉干</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -7686,19 +7686,19 @@
         <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H162" t="n">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7725,41 +7725,41 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C163" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7770,25 +7770,25 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C164" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
         <v>1</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H164" t="n">
@@ -7800,11 +7800,11 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C165" t="n">
         <v>3</v>
@@ -7833,82 +7833,82 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>6</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="H165" t="n">
-        <v>2</v>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J165" t="n">
-        <v>4</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C166" t="n">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="D166" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J166" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
@@ -7919,44 +7919,44 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -7964,113 +7964,113 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>1</v>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>2</v>
       </c>
       <c r="C170" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -8081,17 +8081,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -8099,27 +8099,27 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -8130,13 +8130,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C172" t="n">
         <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -8144,11 +8144,11 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H172" t="n">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8175,17 +8175,17 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -8193,23 +8193,23 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -8220,55 +8220,55 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C174" t="n">
         <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C175" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -8291,36 +8291,36 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C176" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H176" t="n">
@@ -8344,40 +8344,40 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C177" t="n">
         <v>3</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -8385,77 +8385,77 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>翼风</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B178" t="n">
+        <v>9</v>
+      </c>
+      <c r="C178" t="n">
+        <v>6</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>6</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>2</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
         <v>7</v>
       </c>
-      <c r="C178" t="n">
-        <v>129</v>
-      </c>
-      <c r="D178" t="n">
-        <v>60</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>73.3%</t>
-        </is>
-      </c>
-      <c r="F178" t="n">
-        <v>69</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>65.2%</t>
-        </is>
-      </c>
-      <c r="H178" t="n">
-        <v>11</v>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>81.8%</t>
-        </is>
-      </c>
-      <c r="J178" t="n">
-        <v>35</v>
-      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>艺术家</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>10</v>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H179" t="n">
@@ -8475,25 +8475,25 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C180" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -8504,19 +8504,19 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J180" t="n">
@@ -8524,104 +8524,104 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>翼风</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>91.4%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>艺术家</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C182" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J182" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -8631,19 +8631,19 @@
         <v>6</v>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H183" t="n">
@@ -8651,29 +8651,29 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C184" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -8684,72 +8684,72 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D185" t="n">
         <v>1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J185" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -8760,29 +8760,29 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C186" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D186" t="n">
         <v>1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -8790,67 +8790,67 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>谢朵儿</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>谢朵儿</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C188" t="n">
         <v>3</v>
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -8891,25 +8891,25 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C189" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -8917,11 +8917,11 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -8936,7 +8936,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>谢朵儿</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -8958,15 +8958,15 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -8974,14 +8974,14 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>谢朵儿</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -9007,19 +9007,19 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -9030,33 +9030,33 @@
         </is>
       </c>
       <c r="B192" t="n">
+        <v>2</v>
+      </c>
+      <c r="C192" t="n">
         <v>10</v>
       </c>
-      <c r="C192" t="n">
+      <c r="D192" t="n">
+        <v>4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
         <v>6</v>
       </c>
-      <c r="D192" t="n">
-        <v>2</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F192" t="n">
-        <v>4</v>
-      </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -9075,25 +9075,25 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C193" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H193" t="n">
@@ -9105,85 +9105,85 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C194" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C195" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D195" t="n">
+        <v>2</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
         <v>4</v>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F195" t="n">
-        <v>5</v>
-      </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H195" t="n">
@@ -9191,11 +9191,11 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -9206,119 +9206,119 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C196" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D196" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>钟杰</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B197" t="n">
+        <v>6</v>
+      </c>
+      <c r="C197" t="n">
+        <v>39</v>
+      </c>
+      <c r="D197" t="n">
         <v>11</v>
       </c>
-      <c r="C197" t="n">
-        <v>3</v>
-      </c>
-      <c r="D197" t="n">
-        <v>2</v>
-      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>阿函</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H198" t="n">
@@ -9326,93 +9326,93 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C199" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>钟杰</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C200" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -9420,28 +9420,28 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>阿函</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C201" t="n">
         <v>3</v>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -9449,27 +9449,27 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -9480,21 +9480,21 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C202" t="n">
         <v>3</v>
       </c>
       <c r="D202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -9525,33 +9525,33 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C203" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D203" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -9566,11 +9566,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>雨神末路</t>
+          <t>陈俊洁</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C204" t="n">
         <v>3</v>
@@ -9592,62 +9592,197 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>8</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3</v>
+      </c>
+      <c r="D205" t="n">
+        <v>2</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>2</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>9</v>
+      </c>
+      <c r="C206" t="n">
+        <v>20</v>
+      </c>
+      <c r="D206" t="n">
+        <v>12</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>8</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>3</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>10</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>雨神末路</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>11</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>2</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
           <t>鼓鼓</t>
         </is>
       </c>
-      <c r="B205" t="n">
+      <c r="B208" t="n">
         <v>10</v>
       </c>
-      <c r="C205" t="n">
-        <v>3</v>
-      </c>
-      <c r="D205" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F205" t="n">
-        <v>2</v>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H205" t="n">
-        <v>0</v>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J205" t="n">
+      <c r="C208" t="n">
+        <v>3</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>2</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
         <v>4</v>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="K208" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>

--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,38 +483,38 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2013,26 +2013,26 @@
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2040,11 +2040,11 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -3453,22 +3453,22 @@
         <v>12</v>
       </c>
       <c r="C68" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -3480,11 +3480,11 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>86.2%</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
         <v>11</v>
       </c>
       <c r="C83" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D83" t="n">
         <v>5</v>
@@ -4139,27 +4139,27 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -4443,38 +4443,38 @@
         <v>8</v>
       </c>
       <c r="C90" t="n">
+        <v>9</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
         <v>6</v>
       </c>
-      <c r="D90" t="n">
-        <v>3</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>3</v>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -5208,38 +5208,38 @@
         <v>4</v>
       </c>
       <c r="C107" t="n">
+        <v>24</v>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
         <v>21</v>
       </c>
-      <c r="D107" t="n">
-        <v>3</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>18</v>
-      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5973,22 +5973,22 @@
         <v>9</v>
       </c>
       <c r="C124" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -7548,38 +7548,38 @@
         <v>5</v>
       </c>
       <c r="C159" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D159" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>7</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
           <t>57.1%</t>
         </is>
       </c>
-      <c r="H159" t="n">
-        <v>6</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="J159" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7998,22 +7998,22 @@
         <v>1</v>
       </c>
       <c r="C169" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D169" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="H169" t="n">
@@ -8025,11 +8025,11 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -8268,22 +8268,22 @@
         <v>10</v>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H175" t="n">
@@ -9303,26 +9303,26 @@
         <v>7</v>
       </c>
       <c r="C198" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -9330,11 +9330,11 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -9528,38 +9528,38 @@
         <v>6</v>
       </c>
       <c r="C203" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D203" t="n">
+        <v>8</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
         <v>7</v>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="F203" t="n">
-        <v>5</v>
-      </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J203" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>

--- a/data/粤小座位号数据统计.xlsx
+++ b/data/粤小座位号数据统计.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:K210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -629,27 +629,27 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -2519,11 +2519,11 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2535,11 +2535,11 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
         <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D59" t="n">
         <v>2</v>
@@ -3059,27 +3059,27 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -3183,22 +3183,22 @@
         <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D62" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -3453,22 +3453,22 @@
         <v>12</v>
       </c>
       <c r="C68" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D68" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -3716,45 +3716,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>妹妹</t>
+          <t>天时</t>
         </is>
       </c>
       <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
         <v>4</v>
       </c>
-      <c r="C74" t="n">
-        <v>4</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>3</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>2</v>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
         <v>4</v>
@@ -3783,37 +3783,37 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>宁自</t>
+          <t>妹妹</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>5</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -3824,27 +3824,27 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3855,13 +3855,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C77" t="n">
         <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3869,15 +3869,15 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3885,28 +3885,28 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>宝儿姐</t>
+          <t>宁自</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3918,11 +3918,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3945,13 +3945,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3986,17 +3986,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>小一凡</t>
+          <t>宝儿姐</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C80" t="n">
         <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4004,27 +4004,27 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
@@ -4049,15 +4049,15 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -4080,29 +4080,29 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4125,58 +4125,58 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C83" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
         <v>5</v>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>25</v>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>小宇</t>
+          <t>小一凡</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4184,41 +4184,41 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>小希</t>
+          <t>小宇</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -4229,15 +4229,15 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4245,11 +4245,11 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4260,13 +4260,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="n">
         <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4274,15 +4274,15 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
         <v>3</v>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -4335,18 +4335,18 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>小希</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -4356,19 +4356,19 @@
         <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -4380,11 +4380,11 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4395,41 +4395,41 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4440,41 +4440,41 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -4485,41 +4485,41 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>8</v>
+      </c>
+      <c r="C91" t="n">
         <v>9</v>
       </c>
-      <c r="C91" t="n">
-        <v>23</v>
-      </c>
       <c r="D91" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -4530,41 +4530,41 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>9</v>
+      </c>
+      <c r="C92" t="n">
+        <v>23</v>
+      </c>
+      <c r="D92" t="n">
         <v>10</v>
       </c>
-      <c r="C92" t="n">
-        <v>16</v>
-      </c>
-      <c r="D92" t="n">
-        <v>4</v>
-      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -4575,86 +4575,86 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C93" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>小张哥</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B94" t="n">
+        <v>11</v>
+      </c>
+      <c r="C94" t="n">
+        <v>18</v>
+      </c>
+      <c r="D94" t="n">
         <v>10</v>
       </c>
-      <c r="C94" t="n">
-        <v>4</v>
-      </c>
-      <c r="D94" t="n">
-        <v>2</v>
-      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4665,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -4695,11 +4695,11 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4732,36 +4732,36 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>小杀宝贝</t>
+          <t>小张哥</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4769,11 +4769,11 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4822,33 +4822,33 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>小樱</t>
+          <t>小杀宝贝</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4859,11 +4859,11 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -4875,36 +4875,36 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>小猪</t>
+          <t>小樱</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4920,11 +4920,11 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4935,25 +4935,25 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -4965,11 +4965,11 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4980,41 +4980,41 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C102" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="D102" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -5025,58 +5025,58 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>小白宝宝</t>
+          <t>小猪</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5084,11 +5084,11 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -5100,11 +5100,11 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5115,41 +5115,41 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F105" t="n">
-        <v>9</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>77.8%</t>
-        </is>
-      </c>
       <c r="H105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -5160,41 +5160,41 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C106" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="D106" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -5205,33 +5205,33 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C107" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>26</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>3</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>21</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>38.1%</t>
-        </is>
-      </c>
-      <c r="H107" t="n">
-        <v>12</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>41.7%</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -5250,41 +5250,41 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D108" t="n">
         <v>3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
     </row>
@@ -5295,41 +5295,41 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5340,41 +5340,41 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -5385,13 +5385,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5399,44 +5399,44 @@
         </is>
       </c>
       <c r="F111" t="n">
+        <v>3</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
         <v>4</v>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>3</v>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>小米粥</t>
+          <t>小白宝宝</t>
         </is>
       </c>
       <c r="B112" t="n">
+        <v>11</v>
+      </c>
+      <c r="C112" t="n">
         <v>5</v>
       </c>
-      <c r="C112" t="n">
-        <v>2</v>
-      </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5444,11 +5444,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -5475,25 +5475,25 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C113" t="n">
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -5505,40 +5505,40 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>小蓉</t>
+          <t>小米粥</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -5550,11 +5550,11 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C115" t="n">
         <v>3</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -5606,17 +5606,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>小鲜</t>
+          <t>小蓉</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C116" t="n">
         <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -5624,23 +5624,23 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -5651,29 +5651,29 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>徐言雨</t>
+          <t>小鲜</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C117" t="n">
         <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -5696,45 +5696,45 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>木易</t>
+          <t>徐言雨</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C118" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5745,41 +5745,41 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119" t="n">
+        <v>13</v>
+      </c>
+      <c r="D119" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>8</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
         <v>6</v>
       </c>
-      <c r="D119" t="n">
-        <v>2</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>4</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H119" t="n">
-        <v>2</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>4</v>
-      </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5790,41 +5790,41 @@
         </is>
       </c>
       <c r="B120" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" t="n">
+        <v>6</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
         <v>4</v>
       </c>
-      <c r="C120" t="n">
-        <v>9</v>
-      </c>
-      <c r="D120" t="n">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>2</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
         <v>4</v>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>5</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="H120" t="n">
-        <v>2</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>5</v>
-      </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5835,41 +5835,41 @@
         </is>
       </c>
       <c r="B121" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" t="n">
+        <v>9</v>
+      </c>
+      <c r="D121" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
         <v>5</v>
       </c>
-      <c r="C121" t="n">
-        <v>2</v>
-      </c>
-      <c r="D121" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>1</v>
-      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -5880,21 +5880,21 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -5925,41 +5925,41 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C123" t="n">
         <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5970,41 +5970,41 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C124" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6015,41 +6015,41 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C125" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D125" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -6060,41 +6060,41 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6105,62 +6105,62 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>李忆彤</t>
+          <t>木易</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -6168,19 +6168,19 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -6195,41 +6195,41 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
@@ -6254,27 +6254,27 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6285,25 +6285,25 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C131" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -6315,40 +6315,40 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>李靖</t>
+          <t>李忆彤</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C133" t="n">
         <v>3</v>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -6397,11 +6397,11 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -6409,24 +6409,24 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>林花花</t>
+          <t>李靖</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>4</v>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="B135" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" t="n">
         <v>5</v>
       </c>
-      <c r="C135" t="n">
-        <v>3</v>
-      </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -6479,27 +6479,27 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -6510,13 +6510,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -6524,11 +6524,11 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -6540,11 +6540,11 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -6555,13 +6555,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -6585,11 +6585,11 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6600,86 +6600,86 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C138" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>3</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F138" t="n">
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
         <v>9</v>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="K138" t="inlineStr">
         <is>
           <t>55.6%</t>
-        </is>
-      </c>
-      <c r="H138" t="n">
-        <v>2</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J138" t="n">
-        <v>8</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>桃子</t>
+          <t>林花花</t>
         </is>
       </c>
       <c r="B139" t="n">
+        <v>11</v>
+      </c>
+      <c r="C139" t="n">
+        <v>15</v>
+      </c>
+      <c r="D139" t="n">
         <v>5</v>
       </c>
-      <c r="C139" t="n">
-        <v>55</v>
-      </c>
-      <c r="D139" t="n">
-        <v>22</v>
-      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -6690,58 +6690,58 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -6765,11 +6765,11 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6780,13 +6780,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C142" t="n">
         <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -6794,11 +6794,11 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H142" t="n">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6825,33 +6825,33 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C143" t="n">
         <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -6884,19 +6884,19 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6915,13 +6915,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C145" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -6929,11 +6929,11 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H145" t="n">
@@ -6945,11 +6945,11 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D146" t="n">
         <v>1</v>
@@ -6974,15 +6974,15 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -6990,40 +6990,40 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>水瓶座</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C147" t="n">
         <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7050,21 +7050,21 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C148" t="n">
         <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -7076,15 +7076,15 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C149" t="n">
         <v>3</v>
@@ -7113,11 +7113,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -7125,11 +7125,11 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -7140,41 +7140,41 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C150" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7185,41 +7185,41 @@
         </is>
       </c>
       <c r="B151" t="n">
+        <v>10</v>
+      </c>
+      <c r="C151" t="n">
+        <v>32</v>
+      </c>
+      <c r="D151" t="n">
         <v>11</v>
       </c>
-      <c r="C151" t="n">
-        <v>3</v>
-      </c>
-      <c r="D151" t="n">
-        <v>0</v>
-      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -7230,13 +7230,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C152" t="n">
         <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -7244,19 +7244,19 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -7271,25 +7271,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>泡泡堂主</t>
+          <t>水瓶座</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -7305,67 +7305,67 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>浮玉</t>
+          <t>泡泡堂主</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C154" t="n">
         <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>溏心蛋</t>
+          <t>浮玉</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C155" t="n">
         <v>3</v>
@@ -7383,23 +7383,23 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7410,55 +7410,55 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -7469,11 +7469,11 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H157" t="n">
@@ -7485,56 +7485,56 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>满满mio</t>
+          <t>溏心蛋</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C158" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7545,41 +7545,41 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7590,41 +7590,41 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C160" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D160" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -7635,148 +7635,148 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C161" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D161" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>牛肉干</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>满满mio</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C163" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D163" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>王予初</t>
+          <t>牛肉干</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -7815,17 +7815,17 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -7845,11 +7845,11 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7860,41 +7860,41 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
         <v>1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J166" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7905,41 +7905,41 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C167" t="n">
         <v>6</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -7964,89 +7964,89 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C169" t="n">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="D169" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>王正刚</t>
+          <t>王予初</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C170" t="n">
         <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -8054,27 +8054,27 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8085,52 +8085,52 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C172" t="n">
         <v>3</v>
@@ -8148,68 +8148,68 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>田鸡</t>
+          <t>王正刚</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C173" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -8220,13 +8220,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C174" t="n">
         <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H174" t="n">
@@ -8250,11 +8250,11 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8265,41 +8265,41 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C175" t="n">
         <v>6</v>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F175" t="n">
+        <v>3</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>3</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
         <v>4</v>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H175" t="n">
-        <v>2</v>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J175" t="n">
-        <v>1</v>
-      </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C176" t="n">
         <v>3</v>
@@ -8328,23 +8328,23 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -8355,21 +8355,21 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -8377,11 +8377,11 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -8389,21 +8389,21 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C178" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -8414,56 +8414,56 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>白川</t>
+          <t>田鸡</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C179" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H179" t="n">
@@ -8475,11 +8475,11 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -8504,83 +8504,83 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>翼风</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C181" t="n">
-        <v>131</v>
+        <v>6</v>
       </c>
       <c r="D181" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>艺术家</t>
+          <t>白川</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C182" t="n">
         <v>3</v>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8610,67 +8610,67 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>翼风</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C183" t="n">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="D183" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>范一月</t>
+          <t>艺术家</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C184" t="n">
         <v>3</v>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H184" t="n">
@@ -8700,11 +8700,11 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -8715,131 +8715,131 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C185" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H185" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
         <v>4</v>
       </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J185" t="n">
-        <v>11</v>
-      </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C186" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F186" t="n">
+        <v>3</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
         <v>5</v>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="H186" t="n">
-        <v>1</v>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J186" t="n">
-        <v>6</v>
-      </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>萧何</t>
+          <t>范一月</t>
         </is>
       </c>
       <c r="B187" t="n">
+        <v>11</v>
+      </c>
+      <c r="C187" t="n">
         <v>9</v>
       </c>
-      <c r="C187" t="n">
-        <v>6</v>
-      </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -8850,25 +8850,25 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D188" t="n">
         <v>1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H188" t="n">
@@ -8880,11 +8880,11 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8895,13 +8895,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -8917,48 +8917,48 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J189" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>谢朵儿</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C190" t="n">
         <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H190" t="n">
@@ -8966,26 +8966,26 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>谢朵儿</t>
+          <t>萧何</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C191" t="n">
         <v>3</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -9015,73 +9015,73 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>谢朵儿</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C192" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>豪哥哥</t>
+          <t>谢朵儿</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C193" t="n">
         <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -9089,15 +9089,15 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -9105,11 +9105,11 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -9142,19 +9142,19 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -9165,41 +9165,41 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C195" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D195" t="n">
         <v>2</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -9210,131 +9210,131 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C196" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B197" t="n">
+        <v>10</v>
+      </c>
+      <c r="C197" t="n">
         <v>6</v>
       </c>
-      <c r="C197" t="n">
-        <v>39</v>
-      </c>
       <c r="D197" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>郭小炜</t>
+          <t>豪哥哥</t>
         </is>
       </c>
       <c r="B198" t="n">
+        <v>12</v>
+      </c>
+      <c r="C198" t="n">
         <v>7</v>
       </c>
-      <c r="C198" t="n">
-        <v>12</v>
-      </c>
       <c r="D198" t="n">
+        <v>3</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>4</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
         <v>5</v>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="F198" t="n">
-        <v>7</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="H198" t="n">
-        <v>3</v>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J198" t="n">
-        <v>7</v>
-      </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -9345,156 +9345,156 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C199" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D199" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>钟杰</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J200" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>阿函</t>
+          <t>郭小炜</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>钟杰</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C202" t="n">
         <v>3</v>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -9521,45 +9521,45 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>陈俊洁</t>
+          <t>阿函</t>
         </is>
       </c>
       <c r="B203" t="n">
+        <v>12</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>3</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>2</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
         <v>6</v>
       </c>
-      <c r="C203" t="n">
-        <v>15</v>
-      </c>
-      <c r="D203" t="n">
-        <v>8</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F203" t="n">
-        <v>7</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="H203" t="n">
-        <v>2</v>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J203" t="n">
-        <v>13</v>
-      </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C204" t="n">
         <v>3</v>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -9592,15 +9592,15 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -9615,41 +9615,41 @@
         </is>
       </c>
       <c r="B205" t="n">
+        <v>6</v>
+      </c>
+      <c r="C205" t="n">
+        <v>15</v>
+      </c>
+      <c r="D205" t="n">
         <v>8</v>
       </c>
-      <c r="C205" t="n">
-        <v>3</v>
-      </c>
-      <c r="D205" t="n">
-        <v>2</v>
-      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J205" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -9660,66 +9660,66 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C206" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D206" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>雨神末路</t>
+          <t>陈俊洁</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C207" t="n">
         <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -9735,54 +9735,144 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
+          <t>陈俊洁</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>9</v>
+      </c>
+      <c r="C208" t="n">
+        <v>20</v>
+      </c>
+      <c r="D208" t="n">
+        <v>12</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>8</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>3</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>10</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>雨神末路</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>11</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
           <t>鼓鼓</t>
         </is>
       </c>
-      <c r="B208" t="n">
+      <c r="B210" t="n">
         <v>10</v>
       </c>
-      <c r="C208" t="n">
-        <v>3</v>
-      </c>
-      <c r="D208" t="n">
-        <v>1</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F208" t="n">
-        <v>2</v>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H208" t="n">
-        <v>0</v>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J208" t="n">
+      <c r="C210" t="n">
+        <v>3</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
         <v>4</v>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="K210" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
